--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2245-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2245-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{444B8487-84A2-441F-B0C3-CE2DACB5DF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCB09AB0-E3F4-4561-9B41-E941CDC157A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{15454C95-1960-450E-AA20-72D41494A00B}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{042025B3-0CEE-4837-A28E-98077C9A3A6C}"/>
   </bookViews>
   <sheets>
     <sheet name="2245-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1478,24 +1478,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2C8298-6D13-498E-A1A0-63E222A4F123}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10986566-5D07-41D6-A813-6858F398DA70}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1528,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1565,7 +1564,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1617,7 +1616,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1685,7 +1684,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="13" t="s">
@@ -1785,7 +1784,7 @@
       <c r="W6" s="46"/>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2023</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>2022</v>
       </c>
@@ -1929,7 +1928,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>2021</v>
       </c>
@@ -2001,7 +2000,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>2020</v>
       </c>
@@ -2073,7 +2072,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2019</v>
       </c>
@@ -2145,7 +2144,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
         <v>2018</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>2017</v>
       </c>
@@ -2289,7 +2288,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>2016</v>
       </c>
@@ -2361,7 +2360,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>38</v>
       </c>
